--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T15:20:56+00:00</t>
+    <t>2026-10-09T06:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T06:09:27+00:00</t>
+    <t>2026-10-09T08:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:15:54+00:00</t>
+    <t>2026-10-09T08:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T08:42:14+00:00</t>
+    <t>2026-10-09T09:07:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:07:37+00:00</t>
+    <t>2026-10-09T12:41:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T12:41:54+00:00</t>
+    <t>2026-10-12T13:54:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:54:53+00:00</t>
+    <t>2026-10-12T14:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:06:36+00:00</t>
+    <t>2026-10-12T14:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T14:31:02+00:00</t>
+    <t>2026-10-13T07:15:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T07:15:40+00:00</t>
+    <t>2026-10-14T06:31:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T06:31:33+00:00</t>
+    <t>2026-10-15T07:03:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-main/ValueSet-at-ediag-condition-clinical-status-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T07:03:41+00:00</t>
+    <t>2026-10-16T09:08:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
